--- a/MAJSushiConfig/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/MAJSushiConfig/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-doc-vs-participation-type</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-doc-vs-participation-type</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
